--- a/datos/01_Registro_PQR_y_Reclamos_Alimenta_Familia.xlsx
+++ b/datos/01_Registro_PQR_y_Reclamos_Alimenta_Familia.xlsx
@@ -38,7 +38,7 @@
     <t>Genera un dataset simulado de 1.025 PQR de Alimenta Familia (ene-sep 2026) con las columnas indicadas; incluye 64 reportes únicos de salud del lote VEG-BP-2026-047 concentrados tras el 14-abr-2026, 23 reportes de salud que mencionan otros lotes sin respaldo de laboratorio, y errores intencionales documentados (25 duplicados, vacíos, fechas imposibles, tiempos negativos, severidad fuera de escala).</t>
   </si>
   <si>
-    <t>25 duplicados exactos; 12 ciudades vacías; 8 canales vacíos; 10 lotes 'N/D'; 6 fechas imposibles; 7 tiempos de respuesta negativos; 5 severidades = 9 (escala 1-5).</t>
+    <t>25 duplicados exactos; 12 ciudades vacías; 8 canales vacíos; 10 lotes 'N/D'; 6 fechas imposibles; 7 tiempos de respuesta negativos; 5 severidades = 9 (escala 1-5). La columna fecha se guarda como texto a propósito, para conservar las fechas imposibles (p. ej. 2026-13-02).</t>
   </si>
   <si>
     <t>id_pqr</t>
